--- a/artfynd/A 52987-2024 artfynd.xlsx
+++ b/artfynd/A 52987-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123582307</v>
+        <v>123585134</v>
       </c>
       <c r="B2" t="n">
-        <v>57497</v>
+        <v>91603</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>1339</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>555283</v>
+        <v>555354</v>
       </c>
       <c r="R2" t="n">
-        <v>6337935</v>
+        <v>6337904</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-29</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123583447</v>
+        <v>123582307</v>
       </c>
       <c r="B3" t="n">
-        <v>100645</v>
+        <v>57503</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>555342</v>
+        <v>555283</v>
       </c>
       <c r="R3" t="n">
-        <v>6337889</v>
+        <v>6337935</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -858,6 +853,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-29</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123585134</v>
+        <v>123585055</v>
       </c>
       <c r="B4" t="n">
-        <v>91586</v>
+        <v>100662</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1339</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,13 +924,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>555354</v>
+        <v>555353</v>
       </c>
       <c r="R4" t="n">
-        <v>6337904</v>
+        <v>6337923</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -986,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123580546</v>
+        <v>123580885</v>
       </c>
       <c r="B5" t="n">
-        <v>56933</v>
+        <v>91036</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,42 +1002,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102954</v>
+        <v>5321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kulevirke, Kulevirke, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>555271</v>
+        <v>555233</v>
       </c>
       <c r="R5" t="n">
-        <v>6337870</v>
+        <v>6337886</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1093,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123587034</v>
+        <v>123584036</v>
       </c>
       <c r="B6" t="n">
-        <v>57497</v>
+        <v>90983</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1109,21 +1104,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,13 +1128,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>555238</v>
+        <v>555362</v>
       </c>
       <c r="R6" t="n">
-        <v>6337724</v>
+        <v>6337889</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1169,11 +1164,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-29</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1203,7 +1193,7 @@
         <v>123588608</v>
       </c>
       <c r="B7" t="n">
-        <v>57431</v>
+        <v>57437</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1307,10 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123580885</v>
+        <v>123583235</v>
       </c>
       <c r="B8" t="n">
-        <v>91019</v>
+        <v>100662</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1323,21 +1313,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5321</v>
+        <v>222498</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1347,10 +1337,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>555233</v>
+        <v>555286</v>
       </c>
       <c r="R8" t="n">
-        <v>6337886</v>
+        <v>6337897</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1409,10 +1399,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123584263</v>
+        <v>123585849</v>
       </c>
       <c r="B9" t="n">
-        <v>57497</v>
+        <v>91603</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1421,25 +1411,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>1339</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1449,13 +1439,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>555379</v>
+        <v>555354</v>
       </c>
       <c r="R9" t="n">
-        <v>6337897</v>
+        <v>6337851</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1485,11 +1475,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-29</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1516,10 +1501,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123585055</v>
+        <v>123580546</v>
       </c>
       <c r="B10" t="n">
-        <v>100645</v>
+        <v>56939</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1532,37 +1517,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>102954</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Kulevirke, Kulevirke, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>555353</v>
+        <v>555271</v>
       </c>
       <c r="R10" t="n">
-        <v>6337923</v>
+        <v>6337870</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1618,10 +1608,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123584188</v>
+        <v>123580494</v>
       </c>
       <c r="B11" t="n">
-        <v>90966</v>
+        <v>100662</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1630,25 +1620,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1658,13 +1648,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>555378</v>
+        <v>555267</v>
       </c>
       <c r="R11" t="n">
-        <v>6337902</v>
+        <v>6337874</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1720,10 +1710,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123580494</v>
+        <v>123587034</v>
       </c>
       <c r="B12" t="n">
-        <v>100645</v>
+        <v>57503</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1732,25 +1722,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1760,13 +1750,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>555267</v>
+        <v>555238</v>
       </c>
       <c r="R12" t="n">
-        <v>6337874</v>
+        <v>6337724</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1796,6 +1786,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-03-29</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1822,10 +1817,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123583235</v>
+        <v>123583447</v>
       </c>
       <c r="B13" t="n">
-        <v>100645</v>
+        <v>100662</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1862,13 +1857,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>555286</v>
+        <v>555342</v>
       </c>
       <c r="R13" t="n">
-        <v>6337897</v>
+        <v>6337889</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1924,10 +1919,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123584036</v>
+        <v>123580137</v>
       </c>
       <c r="B14" t="n">
-        <v>90966</v>
+        <v>100662</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1936,25 +1931,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1964,13 +1959,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>555362</v>
+        <v>555300</v>
       </c>
       <c r="R14" t="n">
-        <v>6337889</v>
+        <v>6337857</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2026,10 +2021,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123580137</v>
+        <v>123584188</v>
       </c>
       <c r="B15" t="n">
-        <v>100645</v>
+        <v>90983</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2038,25 +2033,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2066,13 +2061,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>555300</v>
+        <v>555378</v>
       </c>
       <c r="R15" t="n">
-        <v>6337857</v>
+        <v>6337902</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2128,10 +2123,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123585849</v>
+        <v>123584263</v>
       </c>
       <c r="B16" t="n">
-        <v>91586</v>
+        <v>57503</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2140,25 +2135,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1339</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2168,13 +2163,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>555354</v>
+        <v>555379</v>
       </c>
       <c r="R16" t="n">
-        <v>6337851</v>
+        <v>6337897</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2204,6 +2199,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-03-29</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2230,10 +2230,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123615027</v>
+        <v>123617443</v>
       </c>
       <c r="B17" t="n">
-        <v>57632</v>
+        <v>57503</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2246,16 +2246,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103020</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2263,29 +2263,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Kulevirke, Kulevirke, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>555318</v>
+        <v>555373</v>
       </c>
       <c r="R17" t="n">
-        <v>6338000</v>
+        <v>6337806</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2315,6 +2306,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-03-30</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2341,10 +2337,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123617822</v>
+        <v>123615027</v>
       </c>
       <c r="B18" t="n">
-        <v>94790</v>
+        <v>57638</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2353,41 +2349,50 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2810</v>
+        <v>103020</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Kulevirke, Kulevirke, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>555397</v>
+        <v>555318</v>
       </c>
       <c r="R18" t="n">
-        <v>6337811</v>
+        <v>6338000</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2443,10 +2448,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123617443</v>
+        <v>123619525</v>
       </c>
       <c r="B19" t="n">
-        <v>57497</v>
+        <v>98396</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2455,25 +2460,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2483,10 +2488,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>555373</v>
+        <v>555292</v>
       </c>
       <c r="R19" t="n">
-        <v>6337806</v>
+        <v>6337747</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2519,11 +2524,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-03-30</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2550,10 +2550,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123619525</v>
+        <v>123617822</v>
       </c>
       <c r="B20" t="n">
-        <v>98379</v>
+        <v>94807</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2562,25 +2562,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>2810</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2590,10 +2590,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>555292</v>
+        <v>555397</v>
       </c>
       <c r="R20" t="n">
-        <v>6337747</v>
+        <v>6337811</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2655,7 +2655,7 @@
         <v>123617733</v>
       </c>
       <c r="B21" t="n">
-        <v>90966</v>
+        <v>90983</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>

--- a/artfynd/A 52987-2024 artfynd.xlsx
+++ b/artfynd/A 52987-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123585134</v>
+        <v>123585055</v>
       </c>
       <c r="B2" t="n">
-        <v>91603</v>
+        <v>100680</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1339</v>
+        <v>222498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>555354</v>
+        <v>555353</v>
       </c>
       <c r="R2" t="n">
-        <v>6337904</v>
+        <v>6337923</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123582307</v>
+        <v>123585849</v>
       </c>
       <c r="B3" t="n">
-        <v>57503</v>
+        <v>91608</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>1339</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>555283</v>
+        <v>555354</v>
       </c>
       <c r="R3" t="n">
-        <v>6337935</v>
+        <v>6337851</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -853,11 +853,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-29</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123585055</v>
+        <v>123580885</v>
       </c>
       <c r="B4" t="n">
-        <v>100662</v>
+        <v>91041</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>5321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,13 +919,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>555353</v>
+        <v>555233</v>
       </c>
       <c r="R4" t="n">
-        <v>6337923</v>
+        <v>6337886</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -986,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123580885</v>
+        <v>123588608</v>
       </c>
       <c r="B5" t="n">
-        <v>91036</v>
+        <v>57440</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,37 +997,42 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5321</v>
+        <v>102621</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kulevirke, Kulevirke, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>555233</v>
+        <v>555263</v>
       </c>
       <c r="R5" t="n">
-        <v>6337886</v>
+        <v>6337883</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1088,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123584036</v>
+        <v>123583447</v>
       </c>
       <c r="B6" t="n">
-        <v>90983</v>
+        <v>100680</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1100,25 +1100,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,13 +1128,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>555362</v>
+        <v>555342</v>
       </c>
       <c r="R6" t="n">
         <v>6337889</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1190,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123588608</v>
+        <v>123585134</v>
       </c>
       <c r="B7" t="n">
-        <v>57437</v>
+        <v>91608</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1206,42 +1206,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102621</v>
+        <v>1339</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Kulevirke, Kulevirke, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>555263</v>
+        <v>555354</v>
       </c>
       <c r="R7" t="n">
-        <v>6337883</v>
+        <v>6337904</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1297,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123583235</v>
+        <v>123584188</v>
       </c>
       <c r="B8" t="n">
-        <v>100662</v>
+        <v>90988</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1309,25 +1304,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1337,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>555286</v>
+        <v>555378</v>
       </c>
       <c r="R8" t="n">
-        <v>6337897</v>
+        <v>6337902</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1399,10 +1394,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123585849</v>
+        <v>123583235</v>
       </c>
       <c r="B9" t="n">
-        <v>91603</v>
+        <v>100680</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1415,21 +1410,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1339</v>
+        <v>222498</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1439,10 +1434,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>555354</v>
+        <v>555286</v>
       </c>
       <c r="R9" t="n">
-        <v>6337851</v>
+        <v>6337897</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1501,10 +1496,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123580546</v>
+        <v>123584263</v>
       </c>
       <c r="B10" t="n">
-        <v>56939</v>
+        <v>57506</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1513,20 +1508,20 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102954</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1535,24 +1530,19 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Kulevirke, Kulevirke, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>555271</v>
+        <v>555379</v>
       </c>
       <c r="R10" t="n">
-        <v>6337870</v>
+        <v>6337897</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1582,6 +1572,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-03-29</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1608,10 +1603,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123580494</v>
+        <v>123580137</v>
       </c>
       <c r="B11" t="n">
-        <v>100662</v>
+        <v>100680</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1648,13 +1643,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>555267</v>
+        <v>555300</v>
       </c>
       <c r="R11" t="n">
-        <v>6337874</v>
+        <v>6337857</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1710,10 +1705,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123587034</v>
+        <v>123580546</v>
       </c>
       <c r="B12" t="n">
-        <v>57503</v>
+        <v>56942</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1722,20 +1717,20 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>102954</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1744,19 +1739,24 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Kulevirke, Kulevirke, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>555238</v>
+        <v>555271</v>
       </c>
       <c r="R12" t="n">
-        <v>6337724</v>
+        <v>6337870</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1786,11 +1786,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-03-29</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1817,10 +1812,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123583447</v>
+        <v>123580494</v>
       </c>
       <c r="B13" t="n">
-        <v>100662</v>
+        <v>100680</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1857,13 +1852,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>555342</v>
+        <v>555267</v>
       </c>
       <c r="R13" t="n">
-        <v>6337889</v>
+        <v>6337874</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1919,10 +1914,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123580137</v>
+        <v>123584036</v>
       </c>
       <c r="B14" t="n">
-        <v>100662</v>
+        <v>90988</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1931,25 +1926,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1959,13 +1954,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>555300</v>
+        <v>555362</v>
       </c>
       <c r="R14" t="n">
-        <v>6337857</v>
+        <v>6337889</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2021,10 +2016,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123584188</v>
+        <v>123582307</v>
       </c>
       <c r="B15" t="n">
-        <v>90983</v>
+        <v>57506</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2037,21 +2032,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2061,10 +2056,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>555378</v>
+        <v>555283</v>
       </c>
       <c r="R15" t="n">
-        <v>6337902</v>
+        <v>6337935</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2097,6 +2092,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-03-29</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2123,10 +2123,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123584263</v>
+        <v>123587034</v>
       </c>
       <c r="B16" t="n">
-        <v>57503</v>
+        <v>57506</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2163,13 +2163,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>555379</v>
+        <v>555238</v>
       </c>
       <c r="R16" t="n">
-        <v>6337897</v>
+        <v>6337724</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2233,7 +2233,7 @@
         <v>123617443</v>
       </c>
       <c r="B17" t="n">
-        <v>57503</v>
+        <v>57506</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2337,10 +2337,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123615027</v>
+        <v>123619525</v>
       </c>
       <c r="B18" t="n">
-        <v>57638</v>
+        <v>98502</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2349,50 +2349,41 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103020</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Kulevirke, Kulevirke, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>555318</v>
+        <v>555292</v>
       </c>
       <c r="R18" t="n">
-        <v>6338000</v>
+        <v>6337747</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2448,10 +2439,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123619525</v>
+        <v>123615027</v>
       </c>
       <c r="B19" t="n">
-        <v>98396</v>
+        <v>57641</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2460,41 +2451,50 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>103020</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Kulevirke, Kulevirke, Sm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>555292</v>
+        <v>555318</v>
       </c>
       <c r="R19" t="n">
-        <v>6337747</v>
+        <v>6338000</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2550,10 +2550,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123617822</v>
+        <v>123617733</v>
       </c>
       <c r="B20" t="n">
-        <v>94807</v>
+        <v>90988</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2562,25 +2562,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2810</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2590,13 +2590,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>555397</v>
+        <v>555387</v>
       </c>
       <c r="R20" t="n">
-        <v>6337811</v>
+        <v>6337818</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2652,10 +2652,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123617733</v>
+        <v>123617822</v>
       </c>
       <c r="B21" t="n">
-        <v>90983</v>
+        <v>94813</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2664,25 +2664,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>2810</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2692,13 +2692,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>555387</v>
+        <v>555397</v>
       </c>
       <c r="R21" t="n">
-        <v>6337818</v>
+        <v>6337811</v>
       </c>
       <c r="S21" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>

--- a/artfynd/A 52987-2024 artfynd.xlsx
+++ b/artfynd/A 52987-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123585055</v>
       </c>
       <c r="B2" t="n">
-        <v>100680</v>
+        <v>100682</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123585849</v>
+        <v>123583447</v>
       </c>
       <c r="B3" t="n">
-        <v>91608</v>
+        <v>100682</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1339</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>555354</v>
+        <v>555342</v>
       </c>
       <c r="R3" t="n">
-        <v>6337851</v>
+        <v>6337889</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123580885</v>
+        <v>123583235</v>
       </c>
       <c r="B4" t="n">
-        <v>91041</v>
+        <v>100682</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5321</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>555233</v>
+        <v>555286</v>
       </c>
       <c r="R4" t="n">
-        <v>6337886</v>
+        <v>6337897</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123588608</v>
+        <v>123584263</v>
       </c>
       <c r="B5" t="n">
-        <v>57440</v>
+        <v>57507</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,20 +993,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102621</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1015,24 +1015,19 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kulevirke, Kulevirke, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>555263</v>
+        <v>555379</v>
       </c>
       <c r="R5" t="n">
-        <v>6337883</v>
+        <v>6337897</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1062,6 +1057,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-03-29</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1088,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123583447</v>
+        <v>123580494</v>
       </c>
       <c r="B6" t="n">
-        <v>100680</v>
+        <v>100682</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1128,13 +1128,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>555342</v>
+        <v>555267</v>
       </c>
       <c r="R6" t="n">
-        <v>6337889</v>
+        <v>6337874</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1190,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123585134</v>
+        <v>123584188</v>
       </c>
       <c r="B7" t="n">
-        <v>91608</v>
+        <v>90990</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1202,25 +1202,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1339</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1230,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>555354</v>
+        <v>555378</v>
       </c>
       <c r="R7" t="n">
-        <v>6337904</v>
+        <v>6337902</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1292,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123584188</v>
+        <v>123584036</v>
       </c>
       <c r="B8" t="n">
-        <v>90988</v>
+        <v>90990</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1332,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>555378</v>
+        <v>555362</v>
       </c>
       <c r="R8" t="n">
-        <v>6337902</v>
+        <v>6337889</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1394,10 +1394,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123583235</v>
+        <v>123587034</v>
       </c>
       <c r="B9" t="n">
-        <v>100680</v>
+        <v>57507</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1406,25 +1406,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1434,13 +1434,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>555286</v>
+        <v>555238</v>
       </c>
       <c r="R9" t="n">
-        <v>6337897</v>
+        <v>6337724</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1470,6 +1470,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-29</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1496,10 +1501,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123584263</v>
+        <v>123585849</v>
       </c>
       <c r="B10" t="n">
-        <v>57506</v>
+        <v>91610</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1508,25 +1513,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>1339</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1536,13 +1541,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>555379</v>
+        <v>555354</v>
       </c>
       <c r="R10" t="n">
-        <v>6337897</v>
+        <v>6337851</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1572,11 +1577,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-03-29</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1603,10 +1603,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123580137</v>
+        <v>123588608</v>
       </c>
       <c r="B11" t="n">
-        <v>100680</v>
+        <v>57441</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1619,37 +1619,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222498</v>
+        <v>102621</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Kulevirke, Kulevirke, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>555300</v>
+        <v>555263</v>
       </c>
       <c r="R11" t="n">
-        <v>6337857</v>
+        <v>6337883</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1705,10 +1710,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123580546</v>
+        <v>123580885</v>
       </c>
       <c r="B12" t="n">
-        <v>56942</v>
+        <v>91043</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1721,42 +1726,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102954</v>
+        <v>5321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Kulevirke, Kulevirke, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>555271</v>
+        <v>555233</v>
       </c>
       <c r="R12" t="n">
-        <v>6337870</v>
+        <v>6337886</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1812,10 +1812,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123580494</v>
+        <v>123582307</v>
       </c>
       <c r="B13" t="n">
-        <v>100680</v>
+        <v>57507</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1824,25 +1824,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1852,13 +1852,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>555267</v>
+        <v>555283</v>
       </c>
       <c r="R13" t="n">
-        <v>6337874</v>
+        <v>6337935</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1888,6 +1888,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-03-29</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1914,10 +1919,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123584036</v>
+        <v>123585134</v>
       </c>
       <c r="B14" t="n">
-        <v>90988</v>
+        <v>91610</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1926,25 +1931,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>1339</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1954,10 +1959,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>555362</v>
+        <v>555354</v>
       </c>
       <c r="R14" t="n">
-        <v>6337889</v>
+        <v>6337904</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2016,10 +2021,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123582307</v>
+        <v>123580546</v>
       </c>
       <c r="B15" t="n">
-        <v>57506</v>
+        <v>56943</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2028,20 +2033,20 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>102954</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2050,19 +2055,24 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Kulevirke, Kulevirke, Sm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>555283</v>
+        <v>555271</v>
       </c>
       <c r="R15" t="n">
-        <v>6337935</v>
+        <v>6337870</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2092,11 +2102,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-03-29</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2123,10 +2128,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123587034</v>
+        <v>123580137</v>
       </c>
       <c r="B16" t="n">
-        <v>57506</v>
+        <v>100682</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2135,25 +2140,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2163,10 +2168,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>555238</v>
+        <v>555300</v>
       </c>
       <c r="R16" t="n">
-        <v>6337724</v>
+        <v>6337857</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2199,11 +2204,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-03-29</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2230,10 +2230,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123617443</v>
+        <v>123615027</v>
       </c>
       <c r="B17" t="n">
-        <v>57506</v>
+        <v>57642</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2246,16 +2246,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>103020</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2263,20 +2263,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Kulevirke, Kulevirke, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>555373</v>
+        <v>555318</v>
       </c>
       <c r="R17" t="n">
-        <v>6337806</v>
+        <v>6338000</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2306,11 +2315,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-03-30</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2337,10 +2341,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123619525</v>
+        <v>123617822</v>
       </c>
       <c r="B18" t="n">
-        <v>98502</v>
+        <v>94815</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2349,25 +2353,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>2810</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2377,10 +2381,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>555292</v>
+        <v>555397</v>
       </c>
       <c r="R18" t="n">
-        <v>6337747</v>
+        <v>6337811</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2439,10 +2443,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123615027</v>
+        <v>123617733</v>
       </c>
       <c r="B19" t="n">
-        <v>57641</v>
+        <v>90990</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2455,46 +2459,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103020</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Kulevirke, Kulevirke, Sm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>555318</v>
+        <v>555387</v>
       </c>
       <c r="R19" t="n">
-        <v>6338000</v>
+        <v>6337818</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2550,10 +2545,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123617733</v>
+        <v>123619525</v>
       </c>
       <c r="B20" t="n">
-        <v>90988</v>
+        <v>98504</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2562,25 +2557,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2590,13 +2585,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>555387</v>
+        <v>555292</v>
       </c>
       <c r="R20" t="n">
-        <v>6337818</v>
+        <v>6337747</v>
       </c>
       <c r="S20" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2652,10 +2647,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123617822</v>
+        <v>123617443</v>
       </c>
       <c r="B21" t="n">
-        <v>94813</v>
+        <v>57507</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2664,25 +2659,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2810</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2692,10 +2687,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>555397</v>
+        <v>555373</v>
       </c>
       <c r="R21" t="n">
-        <v>6337811</v>
+        <v>6337806</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2728,6 +2723,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-03-30</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 52987-2024 artfynd.xlsx
+++ b/artfynd/A 52987-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123585055</v>
+        <v>123583447</v>
       </c>
       <c r="B2" t="n">
         <v>100682</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>555353</v>
+        <v>555342</v>
       </c>
       <c r="R2" t="n">
-        <v>6337923</v>
+        <v>6337889</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123583447</v>
+        <v>123585055</v>
       </c>
       <c r="B3" t="n">
         <v>100682</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>555342</v>
+        <v>555353</v>
       </c>
       <c r="R3" t="n">
-        <v>6337889</v>
+        <v>6337923</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>

--- a/artfynd/A 52987-2024 artfynd.xlsx
+++ b/artfynd/A 52987-2024 artfynd.xlsx
@@ -1919,10 +1919,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123585134</v>
+        <v>123580546</v>
       </c>
       <c r="B14" t="n">
-        <v>91610</v>
+        <v>56943</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1935,37 +1935,42 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1339</v>
+        <v>102954</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Kulevirke, Kulevirke, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>555354</v>
+        <v>555271</v>
       </c>
       <c r="R14" t="n">
-        <v>6337904</v>
+        <v>6337870</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2021,10 +2026,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123580546</v>
+        <v>123585134</v>
       </c>
       <c r="B15" t="n">
-        <v>56943</v>
+        <v>91610</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2037,42 +2042,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>102954</v>
+        <v>1339</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Kulevirke, Kulevirke, Sm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>555271</v>
+        <v>555354</v>
       </c>
       <c r="R15" t="n">
-        <v>6337870</v>
+        <v>6337904</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2545,10 +2545,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123619525</v>
+        <v>123617443</v>
       </c>
       <c r="B20" t="n">
-        <v>98504</v>
+        <v>57507</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2557,25 +2557,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2585,10 +2585,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>555292</v>
+        <v>555373</v>
       </c>
       <c r="R20" t="n">
-        <v>6337747</v>
+        <v>6337806</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2621,6 +2621,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-03-30</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2647,10 +2652,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123617443</v>
+        <v>123619525</v>
       </c>
       <c r="B21" t="n">
-        <v>57507</v>
+        <v>98504</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2659,25 +2664,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2687,10 +2692,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>555373</v>
+        <v>555292</v>
       </c>
       <c r="R21" t="n">
-        <v>6337806</v>
+        <v>6337747</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2723,11 +2728,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-03-30</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 52987-2024 artfynd.xlsx
+++ b/artfynd/A 52987-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123583447</v>
+        <v>123585134</v>
       </c>
       <c r="B2" t="n">
-        <v>100682</v>
+        <v>91610</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>1339</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>555342</v>
+        <v>555354</v>
       </c>
       <c r="R2" t="n">
-        <v>6337889</v>
+        <v>6337904</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123585055</v>
+        <v>123584188</v>
       </c>
       <c r="B3" t="n">
-        <v>100682</v>
+        <v>90990</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>555353</v>
+        <v>555378</v>
       </c>
       <c r="R3" t="n">
-        <v>6337923</v>
+        <v>6337902</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123583235</v>
+        <v>123582307</v>
       </c>
       <c r="B4" t="n">
-        <v>100682</v>
+        <v>57507</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>555286</v>
+        <v>555283</v>
       </c>
       <c r="R4" t="n">
-        <v>6337897</v>
+        <v>6337935</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -955,6 +955,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-29</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -981,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123584263</v>
+        <v>123580494</v>
       </c>
       <c r="B5" t="n">
-        <v>57507</v>
+        <v>100257</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +998,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,13 +1026,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>555379</v>
+        <v>555267</v>
       </c>
       <c r="R5" t="n">
-        <v>6337897</v>
+        <v>6337874</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1057,11 +1062,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-03-29</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1088,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123580494</v>
+        <v>123583235</v>
       </c>
       <c r="B6" t="n">
-        <v>100682</v>
+        <v>100257</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1128,13 +1128,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>555267</v>
+        <v>555286</v>
       </c>
       <c r="R6" t="n">
-        <v>6337874</v>
+        <v>6337897</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1190,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123584188</v>
+        <v>123585055</v>
       </c>
       <c r="B7" t="n">
-        <v>90990</v>
+        <v>100257</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1202,25 +1202,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1230,13 +1230,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>555378</v>
+        <v>555353</v>
       </c>
       <c r="R7" t="n">
-        <v>6337902</v>
+        <v>6337923</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1292,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123584036</v>
+        <v>123583447</v>
       </c>
       <c r="B8" t="n">
-        <v>90990</v>
+        <v>100257</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1304,25 +1304,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1332,13 +1332,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>555362</v>
+        <v>555342</v>
       </c>
       <c r="R8" t="n">
         <v>6337889</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1394,10 +1394,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123587034</v>
+        <v>123585849</v>
       </c>
       <c r="B9" t="n">
-        <v>57507</v>
+        <v>91610</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1406,25 +1406,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>1339</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1434,13 +1434,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>555238</v>
+        <v>555354</v>
       </c>
       <c r="R9" t="n">
-        <v>6337724</v>
+        <v>6337851</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1470,11 +1470,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-29</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1501,10 +1496,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123585849</v>
+        <v>123580885</v>
       </c>
       <c r="B10" t="n">
-        <v>91610</v>
+        <v>91043</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1517,21 +1512,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1339</v>
+        <v>5321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1541,10 +1536,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>555354</v>
+        <v>555233</v>
       </c>
       <c r="R10" t="n">
-        <v>6337851</v>
+        <v>6337886</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1603,10 +1598,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123588608</v>
+        <v>123580546</v>
       </c>
       <c r="B11" t="n">
-        <v>57441</v>
+        <v>56943</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1619,16 +1614,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102621</v>
+        <v>102954</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1648,10 +1643,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>555263</v>
+        <v>555271</v>
       </c>
       <c r="R11" t="n">
-        <v>6337883</v>
+        <v>6337870</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1710,10 +1705,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123580885</v>
+        <v>123587034</v>
       </c>
       <c r="B12" t="n">
-        <v>91043</v>
+        <v>57507</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1722,25 +1717,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5321</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1750,13 +1745,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>555233</v>
+        <v>555238</v>
       </c>
       <c r="R12" t="n">
-        <v>6337886</v>
+        <v>6337724</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1786,6 +1781,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-03-29</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1812,10 +1812,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123582307</v>
+        <v>123584036</v>
       </c>
       <c r="B13" t="n">
-        <v>57507</v>
+        <v>90990</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1828,21 +1828,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1852,10 +1852,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>555283</v>
+        <v>555362</v>
       </c>
       <c r="R13" t="n">
-        <v>6337935</v>
+        <v>6337889</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1888,11 +1888,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-03-29</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1919,10 +1914,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123580546</v>
+        <v>123588608</v>
       </c>
       <c r="B14" t="n">
-        <v>56943</v>
+        <v>57441</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1935,16 +1930,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102954</v>
+        <v>102621</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1964,10 +1959,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>555271</v>
+        <v>555263</v>
       </c>
       <c r="R14" t="n">
-        <v>6337870</v>
+        <v>6337883</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2026,10 +2021,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123585134</v>
+        <v>123584263</v>
       </c>
       <c r="B15" t="n">
-        <v>91610</v>
+        <v>57507</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2038,25 +2033,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1339</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2066,13 +2061,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>555354</v>
+        <v>555379</v>
       </c>
       <c r="R15" t="n">
-        <v>6337904</v>
+        <v>6337897</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2102,6 +2097,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-03-29</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2131,7 +2131,7 @@
         <v>123580137</v>
       </c>
       <c r="B16" t="n">
-        <v>100682</v>
+        <v>100257</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2230,10 +2230,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123615027</v>
+        <v>123617733</v>
       </c>
       <c r="B17" t="n">
-        <v>57642</v>
+        <v>90990</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2246,46 +2246,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103020</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Kulevirke, Kulevirke, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>555318</v>
+        <v>555387</v>
       </c>
       <c r="R17" t="n">
-        <v>6338000</v>
+        <v>6337818</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2341,10 +2332,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123617822</v>
+        <v>123615027</v>
       </c>
       <c r="B18" t="n">
-        <v>94815</v>
+        <v>57642</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2353,41 +2344,50 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2810</v>
+        <v>103020</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Kulevirke, Kulevirke, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>555397</v>
+        <v>555318</v>
       </c>
       <c r="R18" t="n">
-        <v>6337811</v>
+        <v>6338000</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2443,10 +2443,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123617733</v>
+        <v>123617822</v>
       </c>
       <c r="B19" t="n">
-        <v>90990</v>
+        <v>95323</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2455,25 +2455,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>2810</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2483,13 +2483,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>555387</v>
+        <v>555397</v>
       </c>
       <c r="R19" t="n">
-        <v>6337818</v>
+        <v>6337811</v>
       </c>
       <c r="S19" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2655,7 +2655,7 @@
         <v>123619525</v>
       </c>
       <c r="B21" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>

--- a/artfynd/A 52987-2024 artfynd.xlsx
+++ b/artfynd/A 52987-2024 artfynd.xlsx
@@ -1088,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123583235</v>
+        <v>123585849</v>
       </c>
       <c r="B6" t="n">
-        <v>100257</v>
+        <v>91610</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,21 +1104,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>1339</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>555286</v>
+        <v>555354</v>
       </c>
       <c r="R6" t="n">
-        <v>6337897</v>
+        <v>6337851</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1190,7 +1190,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123585055</v>
+        <v>123583235</v>
       </c>
       <c r="B7" t="n">
         <v>100257</v>
@@ -1230,13 +1230,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>555353</v>
+        <v>555286</v>
       </c>
       <c r="R7" t="n">
-        <v>6337923</v>
+        <v>6337897</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123583447</v>
+        <v>123585055</v>
       </c>
       <c r="B8" t="n">
         <v>100257</v>
@@ -1332,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>555342</v>
+        <v>555353</v>
       </c>
       <c r="R8" t="n">
-        <v>6337889</v>
+        <v>6337923</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1394,10 +1394,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123585849</v>
+        <v>123583447</v>
       </c>
       <c r="B9" t="n">
-        <v>91610</v>
+        <v>100257</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1410,21 +1410,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1339</v>
+        <v>222498</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1434,13 +1434,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>555354</v>
+        <v>555342</v>
       </c>
       <c r="R9" t="n">
-        <v>6337851</v>
+        <v>6337889</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -2021,10 +2021,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123584263</v>
+        <v>123580137</v>
       </c>
       <c r="B15" t="n">
-        <v>57507</v>
+        <v>100257</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2033,25 +2033,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2061,13 +2061,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>555379</v>
+        <v>555300</v>
       </c>
       <c r="R15" t="n">
-        <v>6337897</v>
+        <v>6337857</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2097,11 +2097,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-03-29</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2128,10 +2123,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123580137</v>
+        <v>123584263</v>
       </c>
       <c r="B16" t="n">
-        <v>100257</v>
+        <v>57507</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2140,25 +2135,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2168,13 +2163,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>555300</v>
+        <v>555379</v>
       </c>
       <c r="R16" t="n">
-        <v>6337857</v>
+        <v>6337897</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2204,6 +2199,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-03-29</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 52987-2024 artfynd.xlsx
+++ b/artfynd/A 52987-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123585134</v>
+        <v>123585055</v>
       </c>
       <c r="B2" t="n">
-        <v>91610</v>
+        <v>100257</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1339</v>
+        <v>222498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>555354</v>
+        <v>555353</v>
       </c>
       <c r="R2" t="n">
-        <v>6337904</v>
+        <v>6337923</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123584188</v>
+        <v>123580137</v>
       </c>
       <c r="B3" t="n">
-        <v>90990</v>
+        <v>100257</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>555378</v>
+        <v>555300</v>
       </c>
       <c r="R3" t="n">
-        <v>6337902</v>
+        <v>6337857</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123582307</v>
+        <v>123580546</v>
       </c>
       <c r="B4" t="n">
-        <v>57507</v>
+        <v>56943</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,20 +891,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>102954</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -913,19 +913,24 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kulevirke, Kulevirke, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>555283</v>
+        <v>555271</v>
       </c>
       <c r="R4" t="n">
-        <v>6337935</v>
+        <v>6337870</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -955,11 +960,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-29</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -986,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123580494</v>
+        <v>123584188</v>
       </c>
       <c r="B5" t="n">
-        <v>100257</v>
+        <v>90990</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -998,25 +998,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,13 +1026,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>555267</v>
+        <v>555378</v>
       </c>
       <c r="R5" t="n">
-        <v>6337874</v>
+        <v>6337902</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1088,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123585849</v>
+        <v>123584263</v>
       </c>
       <c r="B6" t="n">
-        <v>91610</v>
+        <v>57507</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1100,25 +1100,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1339</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,13 +1128,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>555354</v>
+        <v>555379</v>
       </c>
       <c r="R6" t="n">
-        <v>6337851</v>
+        <v>6337897</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1164,6 +1164,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-29</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1190,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123583235</v>
+        <v>123588608</v>
       </c>
       <c r="B7" t="n">
-        <v>100257</v>
+        <v>57441</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1206,37 +1211,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222498</v>
+        <v>102621</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Kulevirke, Kulevirke, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>555286</v>
+        <v>555263</v>
       </c>
       <c r="R7" t="n">
-        <v>6337897</v>
+        <v>6337883</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1292,10 +1302,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123585055</v>
+        <v>123582307</v>
       </c>
       <c r="B8" t="n">
-        <v>100257</v>
+        <v>57507</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1304,25 +1314,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1332,13 +1342,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>555353</v>
+        <v>555283</v>
       </c>
       <c r="R8" t="n">
-        <v>6337923</v>
+        <v>6337935</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1368,6 +1378,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-29</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1394,10 +1409,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123583447</v>
+        <v>123585134</v>
       </c>
       <c r="B9" t="n">
-        <v>100257</v>
+        <v>91610</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1410,21 +1425,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>1339</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1434,13 +1449,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>555342</v>
+        <v>555354</v>
       </c>
       <c r="R9" t="n">
-        <v>6337889</v>
+        <v>6337904</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1496,10 +1511,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123580885</v>
+        <v>123584036</v>
       </c>
       <c r="B10" t="n">
-        <v>91043</v>
+        <v>90990</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1508,25 +1523,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5321</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1536,10 +1551,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>555233</v>
+        <v>555362</v>
       </c>
       <c r="R10" t="n">
-        <v>6337886</v>
+        <v>6337889</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1598,10 +1613,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123580546</v>
+        <v>123580885</v>
       </c>
       <c r="B11" t="n">
-        <v>56943</v>
+        <v>91043</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1614,42 +1629,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102954</v>
+        <v>5321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Kulevirke, Kulevirke, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>555271</v>
+        <v>555233</v>
       </c>
       <c r="R11" t="n">
-        <v>6337870</v>
+        <v>6337886</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1812,10 +1822,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123584036</v>
+        <v>123580494</v>
       </c>
       <c r="B13" t="n">
-        <v>90990</v>
+        <v>100257</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1824,25 +1834,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1852,13 +1862,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>555362</v>
+        <v>555267</v>
       </c>
       <c r="R13" t="n">
-        <v>6337889</v>
+        <v>6337874</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1914,10 +1924,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123588608</v>
+        <v>123583447</v>
       </c>
       <c r="B14" t="n">
-        <v>57441</v>
+        <v>100257</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1930,42 +1940,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102621</v>
+        <v>222498</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Kulevirke, Kulevirke, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>555263</v>
+        <v>555342</v>
       </c>
       <c r="R14" t="n">
-        <v>6337883</v>
+        <v>6337889</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2021,7 +2026,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123580137</v>
+        <v>123583235</v>
       </c>
       <c r="B15" t="n">
         <v>100257</v>
@@ -2061,13 +2066,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>555300</v>
+        <v>555286</v>
       </c>
       <c r="R15" t="n">
-        <v>6337857</v>
+        <v>6337897</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2123,10 +2128,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123584263</v>
+        <v>123585849</v>
       </c>
       <c r="B16" t="n">
-        <v>57507</v>
+        <v>91610</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2135,25 +2140,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>1339</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2163,13 +2168,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>555379</v>
+        <v>555354</v>
       </c>
       <c r="R16" t="n">
-        <v>6337897</v>
+        <v>6337851</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2199,11 +2204,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-03-29</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2230,10 +2230,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123617733</v>
+        <v>123615027</v>
       </c>
       <c r="B17" t="n">
-        <v>90990</v>
+        <v>57642</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2246,37 +2246,46 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>103020</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Kulevirke, Kulevirke, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>555387</v>
+        <v>555318</v>
       </c>
       <c r="R17" t="n">
-        <v>6337818</v>
+        <v>6338000</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2332,10 +2341,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123615027</v>
+        <v>123619525</v>
       </c>
       <c r="B18" t="n">
-        <v>57642</v>
+        <v>98079</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2344,50 +2353,41 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103020</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Kulevirke, Kulevirke, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>555318</v>
+        <v>555292</v>
       </c>
       <c r="R18" t="n">
-        <v>6338000</v>
+        <v>6337747</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2443,10 +2443,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123617822</v>
+        <v>123617443</v>
       </c>
       <c r="B19" t="n">
-        <v>95323</v>
+        <v>57507</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2455,25 +2455,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2810</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2483,10 +2483,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>555397</v>
+        <v>555373</v>
       </c>
       <c r="R19" t="n">
-        <v>6337811</v>
+        <v>6337806</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2519,6 +2519,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-03-30</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2545,10 +2550,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123617443</v>
+        <v>123617822</v>
       </c>
       <c r="B20" t="n">
-        <v>57507</v>
+        <v>95323</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2557,25 +2562,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>2810</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2585,10 +2590,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>555373</v>
+        <v>555397</v>
       </c>
       <c r="R20" t="n">
-        <v>6337806</v>
+        <v>6337811</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2621,11 +2626,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-03-30</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2652,10 +2652,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123619525</v>
+        <v>123617733</v>
       </c>
       <c r="B21" t="n">
-        <v>98079</v>
+        <v>90990</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2664,25 +2664,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2692,13 +2692,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>555292</v>
+        <v>555387</v>
       </c>
       <c r="R21" t="n">
-        <v>6337747</v>
+        <v>6337818</v>
       </c>
       <c r="S21" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>

--- a/artfynd/A 52987-2024 artfynd.xlsx
+++ b/artfynd/A 52987-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123585055</v>
+        <v>123587034</v>
       </c>
       <c r="B2" t="n">
-        <v>100257</v>
+        <v>57507</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>555353</v>
+        <v>555238</v>
       </c>
       <c r="R2" t="n">
-        <v>6337923</v>
+        <v>6337724</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-29</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123580137</v>
+        <v>123580885</v>
       </c>
       <c r="B3" t="n">
-        <v>100257</v>
+        <v>91043</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>5321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +822,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>555300</v>
+        <v>555233</v>
       </c>
       <c r="R3" t="n">
-        <v>6337857</v>
+        <v>6337886</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123580546</v>
+        <v>123585849</v>
       </c>
       <c r="B4" t="n">
-        <v>56943</v>
+        <v>91610</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,42 +900,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102954</v>
+        <v>1339</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kulevirke, Kulevirke, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>555271</v>
+        <v>555354</v>
       </c>
       <c r="R4" t="n">
-        <v>6337870</v>
+        <v>6337851</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -986,7 +986,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123584188</v>
+        <v>123584036</v>
       </c>
       <c r="B5" t="n">
         <v>90990</v>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>555378</v>
+        <v>555362</v>
       </c>
       <c r="R5" t="n">
-        <v>6337902</v>
+        <v>6337889</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1088,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123584263</v>
+        <v>123580494</v>
       </c>
       <c r="B6" t="n">
-        <v>57507</v>
+        <v>100257</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1100,25 +1100,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,13 +1128,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>555379</v>
+        <v>555267</v>
       </c>
       <c r="R6" t="n">
-        <v>6337897</v>
+        <v>6337874</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1164,11 +1164,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-29</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1195,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123588608</v>
+        <v>123584188</v>
       </c>
       <c r="B7" t="n">
-        <v>57441</v>
+        <v>90990</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1207,46 +1202,41 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102621</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Kulevirke, Kulevirke, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>555263</v>
+        <v>555378</v>
       </c>
       <c r="R7" t="n">
-        <v>6337883</v>
+        <v>6337902</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1302,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123582307</v>
+        <v>123588608</v>
       </c>
       <c r="B8" t="n">
-        <v>57507</v>
+        <v>57441</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1314,20 +1304,20 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>102621</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1336,19 +1326,24 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Kulevirke, Kulevirke, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>555283</v>
+        <v>555263</v>
       </c>
       <c r="R8" t="n">
-        <v>6337935</v>
+        <v>6337883</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1378,11 +1373,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-29</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1409,10 +1399,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123585134</v>
+        <v>123582307</v>
       </c>
       <c r="B9" t="n">
-        <v>91610</v>
+        <v>57507</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1421,25 +1411,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1339</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1449,10 +1439,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>555354</v>
+        <v>555283</v>
       </c>
       <c r="R9" t="n">
-        <v>6337904</v>
+        <v>6337935</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1485,6 +1475,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-29</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1511,10 +1506,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123584036</v>
+        <v>123585134</v>
       </c>
       <c r="B10" t="n">
-        <v>90990</v>
+        <v>91610</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1523,25 +1518,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>1339</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1551,10 +1546,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>555362</v>
+        <v>555354</v>
       </c>
       <c r="R10" t="n">
-        <v>6337889</v>
+        <v>6337904</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1613,10 +1608,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123580885</v>
+        <v>123585055</v>
       </c>
       <c r="B11" t="n">
-        <v>91043</v>
+        <v>100257</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1629,21 +1624,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5321</v>
+        <v>222498</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1653,13 +1648,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>555233</v>
+        <v>555353</v>
       </c>
       <c r="R11" t="n">
-        <v>6337886</v>
+        <v>6337923</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1715,7 +1710,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123587034</v>
+        <v>123584263</v>
       </c>
       <c r="B12" t="n">
         <v>57507</v>
@@ -1755,13 +1750,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>555238</v>
+        <v>555379</v>
       </c>
       <c r="R12" t="n">
-        <v>6337724</v>
+        <v>6337897</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1822,7 +1817,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123580494</v>
+        <v>123583447</v>
       </c>
       <c r="B13" t="n">
         <v>100257</v>
@@ -1862,13 +1857,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>555267</v>
+        <v>555342</v>
       </c>
       <c r="R13" t="n">
-        <v>6337874</v>
+        <v>6337889</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1924,10 +1919,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123583447</v>
+        <v>123580546</v>
       </c>
       <c r="B14" t="n">
-        <v>100257</v>
+        <v>56943</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1940,37 +1935,42 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222498</v>
+        <v>102954</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Kulevirke, Kulevirke, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>555342</v>
+        <v>555271</v>
       </c>
       <c r="R14" t="n">
-        <v>6337889</v>
+        <v>6337870</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2026,7 +2026,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123583235</v>
+        <v>123580137</v>
       </c>
       <c r="B15" t="n">
         <v>100257</v>
@@ -2066,13 +2066,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>555286</v>
+        <v>555300</v>
       </c>
       <c r="R15" t="n">
-        <v>6337897</v>
+        <v>6337857</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2128,10 +2128,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123585849</v>
+        <v>123583235</v>
       </c>
       <c r="B16" t="n">
-        <v>91610</v>
+        <v>100257</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2144,21 +2144,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1339</v>
+        <v>222498</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2168,10 +2168,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>555354</v>
+        <v>555286</v>
       </c>
       <c r="R16" t="n">
-        <v>6337851</v>
+        <v>6337897</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2341,10 +2341,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123619525</v>
+        <v>123617822</v>
       </c>
       <c r="B18" t="n">
-        <v>98079</v>
+        <v>95323</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2353,25 +2353,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>2810</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2381,10 +2381,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>555292</v>
+        <v>555397</v>
       </c>
       <c r="R18" t="n">
-        <v>6337747</v>
+        <v>6337811</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2550,10 +2550,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123617822</v>
+        <v>123619525</v>
       </c>
       <c r="B20" t="n">
-        <v>95323</v>
+        <v>98079</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2562,25 +2562,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2810</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2590,10 +2590,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>555397</v>
+        <v>555292</v>
       </c>
       <c r="R20" t="n">
-        <v>6337811</v>
+        <v>6337747</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>

--- a/artfynd/A 52987-2024 artfynd.xlsx
+++ b/artfynd/A 52987-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123587034</v>
+        <v>123580885</v>
       </c>
       <c r="B2" t="n">
-        <v>57507</v>
+        <v>91043</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>5321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>555238</v>
+        <v>555233</v>
       </c>
       <c r="R2" t="n">
-        <v>6337724</v>
+        <v>6337886</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-29</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123580885</v>
+        <v>123584263</v>
       </c>
       <c r="B3" t="n">
-        <v>91043</v>
+        <v>57507</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5321</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>555233</v>
+        <v>555379</v>
       </c>
       <c r="R3" t="n">
-        <v>6337886</v>
+        <v>6337897</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -858,6 +853,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-29</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123585849</v>
+        <v>123583447</v>
       </c>
       <c r="B4" t="n">
-        <v>91610</v>
+        <v>100257</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1339</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,13 +924,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>555354</v>
+        <v>555342</v>
       </c>
       <c r="R4" t="n">
-        <v>6337851</v>
+        <v>6337889</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -986,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123584036</v>
+        <v>123587034</v>
       </c>
       <c r="B5" t="n">
-        <v>90990</v>
+        <v>57507</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,21 +1002,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,13 +1026,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>555362</v>
+        <v>555238</v>
       </c>
       <c r="R5" t="n">
-        <v>6337889</v>
+        <v>6337724</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1062,6 +1062,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-03-29</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1088,7 +1093,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123580494</v>
+        <v>123583235</v>
       </c>
       <c r="B6" t="n">
         <v>100257</v>
@@ -1128,13 +1133,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>555267</v>
+        <v>555286</v>
       </c>
       <c r="R6" t="n">
-        <v>6337874</v>
+        <v>6337897</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1190,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123584188</v>
+        <v>123585849</v>
       </c>
       <c r="B7" t="n">
-        <v>90990</v>
+        <v>91610</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1202,25 +1207,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>1339</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1230,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>555378</v>
+        <v>555354</v>
       </c>
       <c r="R7" t="n">
-        <v>6337902</v>
+        <v>6337851</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1292,10 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123588608</v>
+        <v>123585055</v>
       </c>
       <c r="B8" t="n">
-        <v>57441</v>
+        <v>100257</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1308,42 +1313,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102621</v>
+        <v>222498</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Kulevirke, Kulevirke, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>555263</v>
+        <v>555353</v>
       </c>
       <c r="R8" t="n">
-        <v>6337883</v>
+        <v>6337923</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1399,10 +1399,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123582307</v>
+        <v>123584036</v>
       </c>
       <c r="B9" t="n">
-        <v>57507</v>
+        <v>90990</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1415,21 +1415,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1439,10 +1439,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>555283</v>
+        <v>555362</v>
       </c>
       <c r="R9" t="n">
-        <v>6337935</v>
+        <v>6337889</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1475,11 +1475,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-29</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1506,10 +1501,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123585134</v>
+        <v>123580137</v>
       </c>
       <c r="B10" t="n">
-        <v>91610</v>
+        <v>100257</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1522,21 +1517,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1339</v>
+        <v>222498</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1546,13 +1541,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>555354</v>
+        <v>555300</v>
       </c>
       <c r="R10" t="n">
-        <v>6337904</v>
+        <v>6337857</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1608,10 +1603,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123585055</v>
+        <v>123588608</v>
       </c>
       <c r="B11" t="n">
-        <v>100257</v>
+        <v>57441</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1624,37 +1619,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222498</v>
+        <v>102621</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Kulevirke, Kulevirke, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>555353</v>
+        <v>555263</v>
       </c>
       <c r="R11" t="n">
-        <v>6337923</v>
+        <v>6337883</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1710,7 +1710,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123584263</v>
+        <v>123582307</v>
       </c>
       <c r="B12" t="n">
         <v>57507</v>
@@ -1750,13 +1750,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>555379</v>
+        <v>555283</v>
       </c>
       <c r="R12" t="n">
-        <v>6337897</v>
+        <v>6337935</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123583447</v>
+        <v>123580494</v>
       </c>
       <c r="B13" t="n">
         <v>100257</v>
@@ -1857,13 +1857,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>555342</v>
+        <v>555267</v>
       </c>
       <c r="R13" t="n">
-        <v>6337889</v>
+        <v>6337874</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1919,10 +1919,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123580546</v>
+        <v>123584188</v>
       </c>
       <c r="B14" t="n">
-        <v>56943</v>
+        <v>90990</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1931,46 +1931,41 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102954</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Kulevirke, Kulevirke, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>555271</v>
+        <v>555378</v>
       </c>
       <c r="R14" t="n">
-        <v>6337870</v>
+        <v>6337902</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2026,10 +2021,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123580137</v>
+        <v>123580546</v>
       </c>
       <c r="B15" t="n">
-        <v>100257</v>
+        <v>56943</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2042,37 +2037,42 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222498</v>
+        <v>102954</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Kulevirke, Kulevirke, Sm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>555300</v>
+        <v>555271</v>
       </c>
       <c r="R15" t="n">
-        <v>6337857</v>
+        <v>6337870</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2128,10 +2128,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123583235</v>
+        <v>123585134</v>
       </c>
       <c r="B16" t="n">
-        <v>100257</v>
+        <v>91610</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2144,21 +2144,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222498</v>
+        <v>1339</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2168,10 +2168,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>555286</v>
+        <v>555354</v>
       </c>
       <c r="R16" t="n">
-        <v>6337897</v>
+        <v>6337904</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2230,10 +2230,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123615027</v>
+        <v>123617822</v>
       </c>
       <c r="B17" t="n">
-        <v>57642</v>
+        <v>95323</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2242,50 +2242,41 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103020</v>
+        <v>2810</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Kulevirke, Kulevirke, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>555318</v>
+        <v>555397</v>
       </c>
       <c r="R17" t="n">
-        <v>6338000</v>
+        <v>6337811</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2341,10 +2332,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123617822</v>
+        <v>123617733</v>
       </c>
       <c r="B18" t="n">
-        <v>95323</v>
+        <v>90990</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2353,25 +2344,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2810</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2381,13 +2372,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>555397</v>
+        <v>555387</v>
       </c>
       <c r="R18" t="n">
-        <v>6337811</v>
+        <v>6337818</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2652,10 +2643,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123617733</v>
+        <v>123615027</v>
       </c>
       <c r="B21" t="n">
-        <v>90990</v>
+        <v>57642</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2668,37 +2659,46 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>103020</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Kulevirke, Kulevirke, Sm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>555387</v>
+        <v>555318</v>
       </c>
       <c r="R21" t="n">
-        <v>6337818</v>
+        <v>6338000</v>
       </c>
       <c r="S21" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>

--- a/artfynd/A 52987-2024 artfynd.xlsx
+++ b/artfynd/A 52987-2024 artfynd.xlsx
@@ -1195,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123585849</v>
+        <v>123585055</v>
       </c>
       <c r="B7" t="n">
-        <v>91610</v>
+        <v>100257</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1211,21 +1211,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1339</v>
+        <v>222498</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1235,13 +1235,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>555354</v>
+        <v>555353</v>
       </c>
       <c r="R7" t="n">
-        <v>6337851</v>
+        <v>6337923</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1297,10 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123585055</v>
+        <v>123585849</v>
       </c>
       <c r="B8" t="n">
-        <v>100257</v>
+        <v>91610</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1313,21 +1313,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222498</v>
+        <v>1339</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1337,13 +1337,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>555353</v>
+        <v>555354</v>
       </c>
       <c r="R8" t="n">
-        <v>6337923</v>
+        <v>6337851</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1710,10 +1710,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123582307</v>
+        <v>123580494</v>
       </c>
       <c r="B12" t="n">
-        <v>57507</v>
+        <v>100257</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1722,25 +1722,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1750,13 +1750,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>555283</v>
+        <v>555267</v>
       </c>
       <c r="R12" t="n">
-        <v>6337935</v>
+        <v>6337874</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1786,11 +1786,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-03-29</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1817,10 +1812,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123580494</v>
+        <v>123582307</v>
       </c>
       <c r="B13" t="n">
-        <v>100257</v>
+        <v>57507</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1829,25 +1824,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1857,13 +1852,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>555267</v>
+        <v>555283</v>
       </c>
       <c r="R13" t="n">
-        <v>6337874</v>
+        <v>6337935</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1893,6 +1888,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-03-29</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 52987-2024 artfynd.xlsx
+++ b/artfynd/A 52987-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123580885</v>
+        <v>123585849</v>
       </c>
       <c r="B2" t="n">
-        <v>91043</v>
+        <v>91610</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5321</v>
+        <v>1339</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>555233</v>
+        <v>555354</v>
       </c>
       <c r="R2" t="n">
-        <v>6337886</v>
+        <v>6337851</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123584263</v>
+        <v>123580494</v>
       </c>
       <c r="B3" t="n">
-        <v>57507</v>
+        <v>100257</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>555379</v>
+        <v>555267</v>
       </c>
       <c r="R3" t="n">
-        <v>6337897</v>
+        <v>6337874</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -853,11 +853,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-29</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -986,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123587034</v>
+        <v>123583235</v>
       </c>
       <c r="B5" t="n">
-        <v>57507</v>
+        <v>100257</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -998,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,13 +1021,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>555238</v>
+        <v>555286</v>
       </c>
       <c r="R5" t="n">
-        <v>6337724</v>
+        <v>6337897</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1062,11 +1057,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-03-29</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123583235</v>
+        <v>123580546</v>
       </c>
       <c r="B6" t="n">
-        <v>100257</v>
+        <v>56943</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1109,37 +1099,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>102954</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Kulevirke, Kulevirke, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>555286</v>
+        <v>555271</v>
       </c>
       <c r="R6" t="n">
-        <v>6337897</v>
+        <v>6337870</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1195,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123585055</v>
+        <v>123585134</v>
       </c>
       <c r="B7" t="n">
-        <v>100257</v>
+        <v>91610</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1211,21 +1206,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222498</v>
+        <v>1339</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1235,13 +1230,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>555353</v>
+        <v>555354</v>
       </c>
       <c r="R7" t="n">
-        <v>6337923</v>
+        <v>6337904</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1297,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123585849</v>
+        <v>123580885</v>
       </c>
       <c r="B8" t="n">
-        <v>91610</v>
+        <v>91043</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1313,21 +1308,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1339</v>
+        <v>5321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1337,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>555354</v>
+        <v>555233</v>
       </c>
       <c r="R8" t="n">
-        <v>6337851</v>
+        <v>6337886</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1399,10 +1394,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123584036</v>
+        <v>123584263</v>
       </c>
       <c r="B9" t="n">
-        <v>90990</v>
+        <v>57507</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1415,21 +1410,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1439,13 +1434,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>555362</v>
+        <v>555379</v>
       </c>
       <c r="R9" t="n">
-        <v>6337889</v>
+        <v>6337897</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1475,6 +1470,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-29</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1501,10 +1501,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123580137</v>
+        <v>123582307</v>
       </c>
       <c r="B10" t="n">
-        <v>100257</v>
+        <v>57507</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1513,25 +1513,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1541,13 +1541,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>555300</v>
+        <v>555283</v>
       </c>
       <c r="R10" t="n">
-        <v>6337857</v>
+        <v>6337935</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1577,6 +1577,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-03-29</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1603,10 +1608,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123588608</v>
+        <v>123585055</v>
       </c>
       <c r="B11" t="n">
-        <v>57441</v>
+        <v>100257</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1619,42 +1624,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102621</v>
+        <v>222498</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Kulevirke, Kulevirke, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>555263</v>
+        <v>555353</v>
       </c>
       <c r="R11" t="n">
-        <v>6337883</v>
+        <v>6337923</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1710,10 +1710,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123580494</v>
+        <v>123587034</v>
       </c>
       <c r="B12" t="n">
-        <v>100257</v>
+        <v>57507</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1722,25 +1722,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1750,13 +1750,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>555267</v>
+        <v>555238</v>
       </c>
       <c r="R12" t="n">
-        <v>6337874</v>
+        <v>6337724</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1786,6 +1786,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-03-29</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1812,10 +1817,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123582307</v>
+        <v>123580137</v>
       </c>
       <c r="B13" t="n">
-        <v>57507</v>
+        <v>100257</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1824,25 +1829,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1852,13 +1857,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>555283</v>
+        <v>555300</v>
       </c>
       <c r="R13" t="n">
-        <v>6337935</v>
+        <v>6337857</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1888,11 +1893,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-03-29</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1919,7 +1919,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123584188</v>
+        <v>123584036</v>
       </c>
       <c r="B14" t="n">
         <v>90990</v>
@@ -1959,10 +1959,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>555378</v>
+        <v>555362</v>
       </c>
       <c r="R14" t="n">
-        <v>6337902</v>
+        <v>6337889</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2021,10 +2021,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123580546</v>
+        <v>123588608</v>
       </c>
       <c r="B15" t="n">
-        <v>56943</v>
+        <v>57441</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2037,16 +2037,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>102954</v>
+        <v>102621</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2066,10 +2066,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>555271</v>
+        <v>555263</v>
       </c>
       <c r="R15" t="n">
-        <v>6337870</v>
+        <v>6337883</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2128,10 +2128,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123585134</v>
+        <v>123584188</v>
       </c>
       <c r="B16" t="n">
-        <v>91610</v>
+        <v>90990</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2140,25 +2140,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1339</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2168,10 +2168,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>555354</v>
+        <v>555378</v>
       </c>
       <c r="R16" t="n">
-        <v>6337904</v>
+        <v>6337902</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2230,10 +2230,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123617822</v>
+        <v>123617733</v>
       </c>
       <c r="B17" t="n">
-        <v>95323</v>
+        <v>90990</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2242,25 +2242,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2810</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2270,13 +2270,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>555397</v>
+        <v>555387</v>
       </c>
       <c r="R17" t="n">
-        <v>6337811</v>
+        <v>6337818</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2332,10 +2332,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123617733</v>
+        <v>123617443</v>
       </c>
       <c r="B18" t="n">
-        <v>90990</v>
+        <v>57507</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2348,21 +2348,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2372,13 +2372,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>555387</v>
+        <v>555373</v>
       </c>
       <c r="R18" t="n">
-        <v>6337818</v>
+        <v>6337806</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2408,6 +2408,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-03-30</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2434,10 +2439,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123617443</v>
+        <v>123619525</v>
       </c>
       <c r="B19" t="n">
-        <v>57507</v>
+        <v>98079</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2446,25 +2451,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2474,10 +2479,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>555373</v>
+        <v>555292</v>
       </c>
       <c r="R19" t="n">
-        <v>6337806</v>
+        <v>6337747</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2510,11 +2515,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-03-30</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2541,10 +2541,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123619525</v>
+        <v>123617822</v>
       </c>
       <c r="B20" t="n">
-        <v>98079</v>
+        <v>95323</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2553,25 +2553,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>2810</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2581,10 +2581,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>555292</v>
+        <v>555397</v>
       </c>
       <c r="R20" t="n">
-        <v>6337747</v>
+        <v>6337811</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>

--- a/artfynd/A 52987-2024 artfynd.xlsx
+++ b/artfynd/A 52987-2024 artfynd.xlsx
@@ -1810,12 +1810,7 @@
         <v>123588608</v>
       </c>
       <c r="B13" t="n">
-        <v>57463</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57725</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 52987-2024 artfynd.xlsx
+++ b/artfynd/A 52987-2024 artfynd.xlsx
@@ -1810,7 +1810,12 @@
         <v>123588608</v>
       </c>
       <c r="B13" t="n">
-        <v>57725</v>
+        <v>57463</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 52987-2024 artfynd.xlsx
+++ b/artfynd/A 52987-2024 artfynd.xlsx
@@ -2757,7 +2757,7 @@
         <v>131755718</v>
       </c>
       <c r="B22" t="n">
-        <v>9412</v>
+        <v>9420</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 52987-2024 artfynd.xlsx
+++ b/artfynd/A 52987-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AY29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3062,6 +3062,578 @@
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>134329426</v>
+      </c>
+      <c r="B25" t="n">
+        <v>9420</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>100575</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Svartoxe</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Ceruchus chrysomelinus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Hochenwarth, 1785)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>frispringande/krypande</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Kulevirke, Sm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>555318</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6337799</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Högsby</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Fågelfors</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>I gammal rödmurken granlåga</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Jonas Hedin</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Jonas Hedin</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>134329599</v>
+      </c>
+      <c r="B26" t="n">
+        <v>5180</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>102204</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Grönhjon</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Callidium aeneum</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(De Geer, 1775)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Kulevirke, Sm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>555253</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6337716</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Högsby</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Fågelfors</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>I Grangren talrika gnag</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Jonas Hedin</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Jonas Hedin</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>134328951</v>
+      </c>
+      <c r="B27" t="n">
+        <v>101388</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Kulevirke, Kulevirke, Sm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>555330</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6337905</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Högsby</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Fågelfors</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Jonas Hedin</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Jonas Hedin</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>134328633</v>
+      </c>
+      <c r="B28" t="n">
+        <v>6287</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>101520</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Större flatbagge</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Peltis grossa</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Kulevirke, Kulevirke, Sm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>555306</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6338005</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Högsby</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Fågelfors</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>I rödmurken granhögstubbe</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Jonas Hedin</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Jonas Hedin</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>134328886</v>
+      </c>
+      <c r="B29" t="n">
+        <v>6287</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>101520</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Större flatbagge</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Peltis grossa</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Kulevirke, Kulevirke, Sm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>555330</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6337905</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Högsby</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Fågelfors</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Talrika hål i grov björk nu liggande som låga</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Jonas Hedin</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Jonas Hedin</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 52987-2024 artfynd.xlsx
+++ b/artfynd/A 52987-2024 artfynd.xlsx
@@ -3398,7 +3398,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>134328633</v>
+        <v>134328886</v>
       </c>
       <c r="B28" t="n">
         <v>6287</v>
@@ -3426,7 +3426,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr">
         <is>
           <t>imago/adult</t>
@@ -3434,7 +3438,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -3448,10 +3452,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>555306</v>
+        <v>555330</v>
       </c>
       <c r="R28" t="n">
-        <v>6338005</v>
+        <v>6337905</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3488,7 +3492,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>I rödmurken granhögstubbe</t>
+          <t>Talrika hål i grov björk nu liggande som låga</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3515,7 +3519,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>134328886</v>
+        <v>134328633</v>
       </c>
       <c r="B29" t="n">
         <v>6287</v>
@@ -3543,11 +3547,7 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
         <is>
           <t>imago/adult</t>
@@ -3555,7 +3555,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -3569,10 +3569,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>555330</v>
+        <v>555306</v>
       </c>
       <c r="R29" t="n">
-        <v>6337905</v>
+        <v>6338005</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3609,7 +3609,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Talrika hål i grov björk nu liggande som låga</t>
+          <t>I rödmurken granhögstubbe</t>
         </is>
       </c>
       <c r="AD29" t="b">

--- a/artfynd/A 52987-2024 artfynd.xlsx
+++ b/artfynd/A 52987-2024 artfynd.xlsx
@@ -3398,7 +3398,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>134328886</v>
+        <v>134328633</v>
       </c>
       <c r="B28" t="n">
         <v>6287</v>
@@ -3426,11 +3426,7 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="K28" t="inlineStr">
         <is>
           <t>imago/adult</t>
@@ -3438,7 +3434,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -3452,10 +3448,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>555330</v>
+        <v>555306</v>
       </c>
       <c r="R28" t="n">
-        <v>6337905</v>
+        <v>6338005</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3492,7 +3488,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Talrika hål i grov björk nu liggande som låga</t>
+          <t>I rödmurken granhögstubbe</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3519,7 +3515,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>134328633</v>
+        <v>134328886</v>
       </c>
       <c r="B29" t="n">
         <v>6287</v>
@@ -3547,7 +3543,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr">
         <is>
           <t>imago/adult</t>
@@ -3555,7 +3555,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -3569,10 +3569,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>555306</v>
+        <v>555330</v>
       </c>
       <c r="R29" t="n">
-        <v>6338005</v>
+        <v>6337905</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3609,7 +3609,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>I rödmurken granhögstubbe</t>
+          <t>Talrika hål i grov björk nu liggande som låga</t>
         </is>
       </c>
       <c r="AD29" t="b">

--- a/artfynd/A 52987-2024 artfynd.xlsx
+++ b/artfynd/A 52987-2024 artfynd.xlsx
@@ -3304,7 +3304,7 @@
         <v>134328951</v>
       </c>
       <c r="B27" t="n">
-        <v>101389</v>
+        <v>101396</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 52987-2024 artfynd.xlsx
+++ b/artfynd/A 52987-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY29"/>
+  <dimension ref="A1:AY30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123580494</v>
+        <v>123584036</v>
       </c>
       <c r="B2" t="n">
-        <v>100279</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>555267</v>
+        <v>555362</v>
       </c>
       <c r="R2" t="n">
-        <v>6337874</v>
+        <v>6337889</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123587034</v>
+        <v>123584188</v>
       </c>
       <c r="B3" t="n">
-        <v>57529</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +807,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>555238</v>
+        <v>555378</v>
       </c>
       <c r="R3" t="n">
-        <v>6337724</v>
+        <v>6337902</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -853,11 +843,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-29</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,37 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123585134</v>
+        <v>123617733</v>
       </c>
       <c r="B4" t="n">
-        <v>91632</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1339</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,13 +904,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>555354</v>
+        <v>555387</v>
       </c>
       <c r="R4" t="n">
-        <v>6337904</v>
+        <v>6337818</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -954,12 +934,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2025-03-30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2025-03-30</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -986,37 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123583447</v>
+        <v>133340174</v>
       </c>
       <c r="B5" t="n">
-        <v>100279</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91974</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>555342</v>
+        <v>555397</v>
       </c>
       <c r="R5" t="n">
-        <v>6337889</v>
+        <v>6337807</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1056,12 +1031,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1088,15 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123585055</v>
+        <v>123585134</v>
       </c>
       <c r="B6" t="n">
-        <v>100279</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92564</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1104,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>1339</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,13 +1098,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>555353</v>
+        <v>555354</v>
       </c>
       <c r="R6" t="n">
-        <v>6337923</v>
+        <v>6337904</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1190,15 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123580885</v>
+        <v>123585849</v>
       </c>
       <c r="B7" t="n">
-        <v>91065</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92564</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1206,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5321</v>
+        <v>1339</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1230,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>555233</v>
+        <v>555354</v>
       </c>
       <c r="R7" t="n">
-        <v>6337886</v>
+        <v>6337851</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1292,37 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123584036</v>
+        <v>123617822</v>
       </c>
       <c r="B8" t="n">
-        <v>91012</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96348</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>2810</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1332,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>555362</v>
+        <v>555397</v>
       </c>
       <c r="R8" t="n">
-        <v>6337889</v>
+        <v>6337811</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1362,12 +1322,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2025-03-30</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2025-03-30</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1394,37 +1354,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123584263</v>
+        <v>123580885</v>
       </c>
       <c r="B9" t="n">
-        <v>57529</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91966</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>5321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1434,13 +1389,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>555379</v>
+        <v>555233</v>
       </c>
       <c r="R9" t="n">
-        <v>6337897</v>
+        <v>6337886</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1470,11 +1425,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-29</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1501,15 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123580137</v>
+        <v>123582307</v>
       </c>
       <c r="B10" t="n">
-        <v>100279</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1517,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1541,13 +1486,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>555300</v>
+        <v>555283</v>
       </c>
       <c r="R10" t="n">
-        <v>6337857</v>
+        <v>6337935</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1577,6 +1522,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-03-29</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1603,15 +1553,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123585849</v>
+        <v>123584263</v>
       </c>
       <c r="B11" t="n">
-        <v>91632</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1619,21 +1564,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1339</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1643,13 +1588,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>555354</v>
+        <v>555379</v>
       </c>
       <c r="R11" t="n">
-        <v>6337851</v>
+        <v>6337897</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1679,6 +1624,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-03-29</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1705,37 +1655,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123584188</v>
+        <v>123587034</v>
       </c>
       <c r="B12" t="n">
-        <v>91012</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1745,13 +1690,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>555378</v>
+        <v>555238</v>
       </c>
       <c r="R12" t="n">
-        <v>6337902</v>
+        <v>6337724</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1781,6 +1726,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-03-29</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1807,15 +1757,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123588608</v>
+        <v>123617443</v>
       </c>
       <c r="B13" t="n">
-        <v>57463</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1823,16 +1768,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102621</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1841,24 +1786,19 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Kulevirke, Kulevirke, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>555263</v>
+        <v>555373</v>
       </c>
       <c r="R13" t="n">
-        <v>6337883</v>
+        <v>6337806</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1882,12 +1822,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2025-03-30</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2025-03-30</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1914,53 +1859,61 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123582307</v>
+        <v>131755718</v>
       </c>
       <c r="B14" t="n">
-        <v>57529</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>9420</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>100575</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svartoxe</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ceruchus chrysomelinus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Hochenwarth, 1785)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Kulevirke, Kulevirke, Sm</t>
+          <t>Leksjöudd, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>555283</v>
+        <v>555378</v>
       </c>
       <c r="R14" t="n">
-        <v>6337935</v>
+        <v>6337911</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1984,17 +1937,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Födosökshack</t>
+          <t>Ca 2 cm stor larv i brunrötad granlåga. Sannolikt svartoxe. Gott om brunrötade granlågor i området. Skogen avverkningsanmäld.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2003,6 +1956,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2021,58 +1975,67 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123580546</v>
+        <v>134329426</v>
       </c>
       <c r="B15" t="n">
-        <v>56965</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>9420</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>102954</v>
+        <v>100575</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Svartoxe</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Ceruchus chrysomelinus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Hochenwarth, 1785)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>frispringande/krypande</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Kulevirke, Kulevirke, Sm</t>
+          <t>Kulevirke, Sm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>555271</v>
+        <v>555318</v>
       </c>
       <c r="R15" t="n">
-        <v>6337870</v>
+        <v>6337799</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2096,12 +2059,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>I gammal rödmurken granlåga</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2116,65 +2084,75 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jonas Hedin</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jonas Hedin</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123583235</v>
+        <v>134328633</v>
       </c>
       <c r="B16" t="n">
-        <v>100279</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>6287</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222498</v>
+        <v>101520</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Större flatbagge</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Peltis grossa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Kulevirke, Kulevirke, Sm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>555286</v>
+        <v>555306</v>
       </c>
       <c r="R16" t="n">
-        <v>6337897</v>
+        <v>6338005</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2198,12 +2176,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>I rödmurken granhögstubbe</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2218,65 +2201,79 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jonas Hedin</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jonas Hedin</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123617822</v>
+        <v>134328886</v>
       </c>
       <c r="B17" t="n">
-        <v>95345</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>6287</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2810</v>
+        <v>101520</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Större flatbagge</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Peltis grossa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Kulevirke, Kulevirke, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>555397</v>
+        <v>555330</v>
       </c>
       <c r="R17" t="n">
-        <v>6337811</v>
+        <v>6337905</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2300,12 +2297,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-03-30</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-03-30</t>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Talrika hål i grov björk nu liggande som låga</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2320,27 +2322,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jonas Hedin</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jonas Hedin</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123615027</v>
+        <v>134329599</v>
       </c>
       <c r="B18" t="n">
-        <v>57664</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5180</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2348,46 +2345,51 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103020</v>
+        <v>102204</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Grönhjon</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(De Geer, 1775)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Kulevirke, Kulevirke, Sm</t>
+          <t>Kulevirke, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>555318</v>
+        <v>555253</v>
       </c>
       <c r="R18" t="n">
-        <v>6338000</v>
+        <v>6337716</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2411,12 +2413,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-03-30</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-03-30</t>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>I Grangren talrika gnag</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2431,27 +2438,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jonas Hedin</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jonas Hedin</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123617733</v>
+        <v>123588608</v>
       </c>
       <c r="B19" t="n">
-        <v>91012</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57794</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2459,37 +2461,42 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>102621</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Kulevirke, Kulevirke, Sm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>555387</v>
+        <v>555263</v>
       </c>
       <c r="R19" t="n">
-        <v>6337818</v>
+        <v>6337883</v>
       </c>
       <c r="S19" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2513,12 +2520,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-03-30</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-03-30</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2545,15 +2552,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123617443</v>
+        <v>123580546</v>
       </c>
       <c r="B20" t="n">
-        <v>57529</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57364</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2561,16 +2563,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>102954</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2579,19 +2581,24 @@
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Kulevirke, Kulevirke, Sm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>555373</v>
+        <v>555271</v>
       </c>
       <c r="R20" t="n">
-        <v>6337806</v>
+        <v>6337870</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2615,17 +2622,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-03-30</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-03-30</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2652,53 +2654,57 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123619525</v>
+        <v>123615027</v>
       </c>
       <c r="B21" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58112</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>103020</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Kulevirke, Kulevirke, Sm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>555292</v>
+        <v>555318</v>
       </c>
       <c r="R21" t="n">
-        <v>6337747</v>
+        <v>6338000</v>
       </c>
       <c r="S21" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2754,61 +2760,48 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131755718</v>
+        <v>123619525</v>
       </c>
       <c r="B22" t="n">
-        <v>9420</v>
+        <v>99118</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100575</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Svartoxe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Ceruchus chrysomelinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hochenwarth, 1785)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Leksjöudd, Sm</t>
+          <t>Kulevirke, Kulevirke, Sm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>555378</v>
+        <v>555292</v>
       </c>
       <c r="R22" t="n">
-        <v>6337911</v>
+        <v>6337747</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2832,17 +2825,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2025-03-30</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ca 2 cm stor larv i brunrötad granlåga. Sannolikt svartoxe. Gott om brunrötade granlågor i området. Skogen avverkningsanmäld.</t>
+          <t>2025-03-30</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2851,7 +2839,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2870,10 +2857,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131885388</v>
+        <v>131882418</v>
       </c>
       <c r="B23" t="n">
-        <v>99106</v>
+        <v>99195</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2905,13 +2892,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>555216</v>
+        <v>555229</v>
       </c>
       <c r="R23" t="n">
-        <v>6337801</v>
+        <v>6337782</v>
       </c>
       <c r="S23" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2967,10 +2954,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131882418</v>
+        <v>131885388</v>
       </c>
       <c r="B24" t="n">
-        <v>99106</v>
+        <v>99195</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3002,13 +2989,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>555229</v>
+        <v>555216</v>
       </c>
       <c r="R24" t="n">
-        <v>6337782</v>
+        <v>6337801</v>
       </c>
       <c r="S24" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3064,67 +3051,48 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>134329426</v>
+        <v>123580137</v>
       </c>
       <c r="B25" t="n">
-        <v>9420</v>
+        <v>101326</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100575</v>
+        <v>222498</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Svartoxe</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Ceruchus chrysomelinus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hochenwarth, 1785)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>frispringande/krypande</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Kulevirke, Sm</t>
+          <t>Kulevirke, Kulevirke, Sm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>555318</v>
+        <v>555300</v>
       </c>
       <c r="R25" t="n">
-        <v>6337799</v>
+        <v>6337857</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3148,17 +3116,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>I gammal rödmurken granlåga</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3173,74 +3136,60 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Jonas Hedin</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Jonas Hedin</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>134329599</v>
+        <v>123580494</v>
       </c>
       <c r="B26" t="n">
-        <v>5180</v>
+        <v>101326</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>102204</v>
+        <v>222498</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Grönhjon</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Kulevirke, Sm</t>
+          <t>Kulevirke, Kulevirke, Sm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>555253</v>
+        <v>555267</v>
       </c>
       <c r="R26" t="n">
-        <v>6337716</v>
+        <v>6337874</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3264,17 +3213,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>I Grangren talrika gnag</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3289,22 +3233,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Jonas Hedin</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Jonas Hedin</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>134328951</v>
+        <v>123583235</v>
       </c>
       <c r="B27" t="n">
-        <v>101396</v>
+        <v>101326</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3336,13 +3280,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>555330</v>
+        <v>555286</v>
       </c>
       <c r="R27" t="n">
-        <v>6337905</v>
+        <v>6337897</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3366,12 +3310,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3386,75 +3330,60 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Jonas Hedin</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Jonas Hedin</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>134328633</v>
+        <v>123583447</v>
       </c>
       <c r="B28" t="n">
-        <v>6287</v>
+        <v>101326</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>101520</v>
+        <v>222498</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Större flatbagge</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Peltis grossa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Kulevirke, Kulevirke, Sm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>555306</v>
+        <v>555342</v>
       </c>
       <c r="R28" t="n">
-        <v>6338005</v>
+        <v>6337889</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3478,17 +3407,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>I rödmurken granhögstubbe</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3503,79 +3427,60 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Jonas Hedin</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Jonas Hedin</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>134328886</v>
+        <v>123585055</v>
       </c>
       <c r="B29" t="n">
-        <v>6287</v>
+        <v>101326</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>101520</v>
+        <v>222498</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Större flatbagge</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Peltis grossa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Kulevirke, Kulevirke, Sm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>555330</v>
+        <v>555353</v>
       </c>
       <c r="R29" t="n">
-        <v>6337905</v>
+        <v>6337923</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3599,17 +3504,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Talrika hål i grov björk nu liggande som låga</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3624,15 +3524,112 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>134328951</v>
+      </c>
+      <c r="B30" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Kulevirke, Kulevirke, Sm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>555330</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6337905</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Högsby</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Fågelfors</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
           <t>Jonas Hedin</t>
         </is>
       </c>
-      <c r="AX29" t="inlineStr">
+      <c r="AX30" t="inlineStr">
         <is>
           <t>Jonas Hedin</t>
         </is>
       </c>
-      <c r="AY29" t="inlineStr"/>
+      <c r="AY30" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 52987-2024 artfynd.xlsx
+++ b/artfynd/A 52987-2024 artfynd.xlsx
@@ -2089,7 +2089,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Jonas Hedin</t>
+          <t>Jonas Hedin, Christian Luth</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>

--- a/artfynd/A 52987-2024 artfynd.xlsx
+++ b/artfynd/A 52987-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY30"/>
+  <dimension ref="A1:AZ30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123584036</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123584188</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123617733</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133340174</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123585134</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123585849</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123617822</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123580885</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1550,6 +1595,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123582307</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1652,6 +1702,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123584263</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1754,6 +1809,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123587034</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1856,6 +1916,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123617443</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1972,6 +2037,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131755718</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2093,6 +2163,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134329426</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2210,6 +2285,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134328633</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2331,6 +2411,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134328886</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2447,6 +2532,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134329599</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2549,6 +2639,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123588608</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2651,6 +2746,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123580546</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2757,6 +2857,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123615027</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2854,6 +2959,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123619525</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2951,6 +3061,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131882418</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3048,6 +3163,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131885388</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3145,6 +3265,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123580137</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3242,6 +3367,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123580494</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3339,6 +3469,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123583235</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3436,6 +3571,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123583447</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3533,6 +3673,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123585055</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3630,8 +3775,44 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134328951</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>